--- a/data/trans_orig/P33B1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P33B1_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que tiene dificultad para dormirse por la noche en 2023</t>
+          <t>Población según la frecuencia con la que tiene dificultad para dormirse por la noche en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61247</t>
+          <t>60894</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90636</t>
+          <t>90508</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>145539</t>
+          <t>144750</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>177930</t>
+          <t>179167</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>214593</t>
+          <t>214136</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>257012</t>
+          <t>256681</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,24%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43215</t>
+          <t>42898</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67823</t>
+          <t>68065</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>102582</t>
+          <t>100490</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>131293</t>
+          <t>129577</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>152821</t>
+          <t>153803</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>189419</t>
+          <t>189474</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>78580</t>
+          <t>76241</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>111873</t>
+          <t>109377</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>179790</t>
+          <t>178333</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>215439</t>
+          <t>212249</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>265381</t>
+          <t>266286</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>314359</t>
+          <t>313950</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>271780</t>
+          <t>274408</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>313334</t>
+          <t>313129</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>258337</t>
+          <t>259035</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>300048</t>
+          <t>302831</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>544551</t>
+          <t>543878</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>604819</t>
+          <t>601678</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,45%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82385</t>
+          <t>85173</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>145946</t>
+          <t>145994</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>117841</t>
+          <t>119987</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>191101</t>
+          <t>192962</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>227263</t>
+          <t>228342</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>328045</t>
+          <t>321994</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68994</t>
+          <t>71421</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>129781</t>
+          <t>131067</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>127445</t>
+          <t>122915</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>205362</t>
+          <t>207540</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>222324</t>
+          <t>225700</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>318701</t>
+          <t>321750</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>284282</t>
+          <t>269948</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>462146</t>
+          <t>466852</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>332553</t>
+          <t>325502</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>521430</t>
+          <t>523364</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>676226</t>
+          <t>684172</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>950465</t>
+          <t>951879</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1574948</t>
+          <t>1576368</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1847922</t>
+          <t>1861801</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1333615</t>
+          <t>1334212</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1649309</t>
+          <t>1678710</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2964402</t>
+          <t>2959255</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3417179</t>
+          <t>3386703</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>74,82%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14794</t>
+          <t>14937</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34724</t>
+          <t>34170</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30122</t>
+          <t>29601</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51011</t>
+          <t>50581</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>49802</t>
+          <t>50896</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>78261</t>
+          <t>79144</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30123</t>
+          <t>31236</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>58201</t>
+          <t>59454</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>40833</t>
+          <t>40165</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>64085</t>
+          <t>64467</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>75908</t>
+          <t>75629</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>112073</t>
+          <t>113366</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>110789</t>
+          <t>109574</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>150940</t>
+          <t>149476</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>131987</t>
+          <t>131016</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>168499</t>
+          <t>168249</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>251641</t>
+          <t>252032</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>304644</t>
+          <t>305163</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,35%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>426299</t>
+          <t>426868</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>475378</t>
+          <t>474376</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>398272</t>
+          <t>399627</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>441510</t>
+          <t>443037</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>839884</t>
+          <t>843033</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>904667</t>
+          <t>907480</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,43%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>168426</t>
+          <t>166757</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>247922</t>
+          <t>250168</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>295691</t>
+          <t>300974</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>403575</t>
+          <t>405716</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>508668</t>
+          <t>502334</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>637711</t>
+          <t>635263</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>154776</t>
+          <t>157883</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>235761</t>
+          <t>234153</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>278517</t>
+          <t>286185</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>381542</t>
+          <t>380465</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>461963</t>
+          <t>468160</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>597656</t>
+          <t>595652</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>487099</t>
+          <t>491136</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>689324</t>
+          <t>690392</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>656006</t>
+          <t>640941</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>873578</t>
+          <t>870229</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1228644</t>
+          <t>1252425</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1527217</t>
+          <t>1536751</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,64%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2311298</t>
+          <t>2308671</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2640786</t>
+          <t>2645662</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2019719</t>
+          <t>2024333</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2426328</t>
+          <t>2442449</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4385822</t>
+          <t>4376076</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4901134</t>
+          <t>4856719</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,39%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33B1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P33B1_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>73872</t>
+          <t>80046</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60894</t>
+          <t>65463</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90508</t>
+          <t>96436</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>161955</t>
+          <t>183670</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>144750</t>
+          <t>164490</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>179167</t>
+          <t>201412</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>235828</t>
+          <t>263716</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>214136</t>
+          <t>240515</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>256681</t>
+          <t>288439</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>54709</t>
+          <t>57784</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42898</t>
+          <t>46069</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68065</t>
+          <t>71261</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>115526</t>
+          <t>125547</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>100490</t>
+          <t>110747</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>129577</t>
+          <t>140320</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>170235</t>
+          <t>183331</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>153803</t>
+          <t>165032</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>189474</t>
+          <t>205944</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>92348</t>
+          <t>100540</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76241</t>
+          <t>85925</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>109377</t>
+          <t>118443</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>196312</t>
+          <t>210879</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>178333</t>
+          <t>191279</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>212249</t>
+          <t>230108</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>288661</t>
+          <t>311419</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>266286</t>
+          <t>288414</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>313950</t>
+          <t>340406</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>294008</t>
+          <t>340159</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>274408</t>
+          <t>316535</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>313129</t>
+          <t>363082</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>279375</t>
+          <t>301220</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>259035</t>
+          <t>280532</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>302831</t>
+          <t>322694</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>573384</t>
+          <t>641379</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>543878</t>
+          <t>605189</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>601678</t>
+          <t>673573</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>48,12%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1268107</t>
+          <t>1399845</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1268107</t>
+          <t>1399845</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1268107</t>
+          <t>1399845</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>118090</t>
+          <t>128162</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85173</t>
+          <t>108180</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>145994</t>
+          <t>154688</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>162552</t>
+          <t>184985</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>119987</t>
+          <t>164618</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>192962</t>
+          <t>207605</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>280642</t>
+          <t>313147</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>228342</t>
+          <t>280304</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>321994</t>
+          <t>347258</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>110425</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71421</t>
+          <t>90866</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>131067</t>
+          <t>134841</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>175198</t>
+          <t>197792</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>122915</t>
+          <t>177821</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>207540</t>
+          <t>223438</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>279541</t>
+          <t>308217</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>225700</t>
+          <t>278745</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>321750</t>
+          <t>344861</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>399732</t>
+          <t>442667</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>269948</t>
+          <t>406250</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>466852</t>
+          <t>485070</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>456012</t>
+          <t>513178</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>325502</t>
+          <t>477648</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>523364</t>
+          <t>548437</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>855744</t>
+          <t>955845</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>684172</t>
+          <t>903566</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>951879</t>
+          <t>1015527</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1667132</t>
+          <t>1548231</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1576368</t>
+          <t>1499356</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1861801</t>
+          <t>1591198</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1443496</t>
+          <t>1274869</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1334212</t>
+          <t>1233356</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1678710</t>
+          <t>1314265</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3110628</t>
+          <t>2823099</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2959255</t>
+          <t>2757039</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3386703</t>
+          <t>2884252</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>65,55%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2289297</t>
+          <t>2229485</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2289297</t>
+          <t>2229485</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2289297</t>
+          <t>2229485</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2237258</t>
+          <t>2170824</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2237258</t>
+          <t>2170824</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2237258</t>
+          <t>2170824</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4526555</t>
+          <t>4400308</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4526555</t>
+          <t>4400308</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4526555</t>
+          <t>4400308</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>23402</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14937</t>
+          <t>18045</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34170</t>
+          <t>38882</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>39213</t>
+          <t>42790</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29601</t>
+          <t>32961</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50581</t>
+          <t>54103</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>62615</t>
+          <t>69862</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50896</t>
+          <t>56431</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>79144</t>
+          <t>87336</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41826</t>
+          <t>45859</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31236</t>
+          <t>33626</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>59454</t>
+          <t>62089</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>51026</t>
+          <t>58540</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>40165</t>
+          <t>46688</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>64467</t>
+          <t>71407</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>92853</t>
+          <t>104399</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>75629</t>
+          <t>86813</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>113366</t>
+          <t>124974</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>128117</t>
+          <t>145464</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>109574</t>
+          <t>124017</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>149476</t>
+          <t>167444</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>149354</t>
+          <t>167821</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>131016</t>
+          <t>149917</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>168249</t>
+          <t>190978</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>277471</t>
+          <t>313286</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>252032</t>
+          <t>286732</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>305163</t>
+          <t>344005</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>453277</t>
+          <t>493192</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>426868</t>
+          <t>468344</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>474376</t>
+          <t>519140</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>420870</t>
+          <t>465726</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>399627</t>
+          <t>439552</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>443037</t>
+          <t>487883</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>874147</t>
+          <t>958917</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>843033</t>
+          <t>925677</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>907480</t>
+          <t>994081</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>68,72%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>215365</t>
+          <t>235280</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>166757</t>
+          <t>207491</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>250168</t>
+          <t>269886</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>363720</t>
+          <t>411445</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>300974</t>
+          <t>382317</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>405716</t>
+          <t>445671</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>579085</t>
+          <t>646724</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>502334</t>
+          <t>606753</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>635263</t>
+          <t>693336</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>200879</t>
+          <t>214067</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>157883</t>
+          <t>187072</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>234153</t>
+          <t>243457</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>341750</t>
+          <t>381879</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>286185</t>
+          <t>353470</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>380465</t>
+          <t>413162</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>542628</t>
+          <t>595947</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>468160</t>
+          <t>555667</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>595652</t>
+          <t>637294</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>620197</t>
+          <t>688672</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>491136</t>
+          <t>636398</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>690392</t>
+          <t>733279</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>801679</t>
+          <t>891878</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>640941</t>
+          <t>849610</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>870229</t>
+          <t>936622</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1421876</t>
+          <t>1580550</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1252425</t>
+          <t>1518563</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1536751</t>
+          <t>1649603</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>22,76%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2414418</t>
+          <t>2381582</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2308671</t>
+          <t>2326886</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2645662</t>
+          <t>2450638</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2143741</t>
+          <t>2041814</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2024333</t>
+          <t>1985858</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2442449</t>
+          <t>2096351</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4558159</t>
+          <t>4423396</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4376076</t>
+          <t>4339489</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4856719</t>
+          <t>4503012</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>62,14%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3450859</t>
+          <t>3519601</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3450859</t>
+          <t>3519601</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3450859</t>
+          <t>3519601</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3650889</t>
+          <t>3727016</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3650889</t>
+          <t>3727016</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3650889</t>
+          <t>3727016</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7101748</t>
+          <t>7246617</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7101748</t>
+          <t>7246617</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7101748</t>
+          <t>7246617</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
